--- a/pipeline/credit_rating/output/visrating_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260924.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-09-24 07:13:24</t>
+          <t>2026-09-24 08:43:44</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">

--- a/pipeline/credit_rating/output/visrating_xhtn_20260924.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20260924.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -958,7 +958,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -2973,7 +2973,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3269,7 +3269,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3565,7 +3565,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3857,7 +3857,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4364,7 +4364,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5045,7 +5045,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5625,7 +5625,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5901,7 +5901,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -5970,7 +5970,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6116,7 +6116,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6578,7 +6578,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6732,7 +6732,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7425,7 +7425,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7656,7 +7656,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7802,7 +7802,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7871,7 +7871,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8017,7 +8017,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8447,7 +8447,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8601,7 +8601,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-09-24 08:43:44</t>
+          <t>2026-09-24 13:44:20</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
